--- a/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
+++ b/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.9</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T11:46:37+00:00</t>
+    <t>2025-11-18T16:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
+++ b/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T16:26:41+00:00</t>
+    <t>2025-11-18T18:41:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
+++ b/currentbuild/ValueSet-NoDomainVitalSignsBloodpressureBodySiteValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T18:41:36+00:00</t>
+    <t>2026-03-18T10:05:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
